--- a/etf_holdings/2026-10-21_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-21_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,46 +451,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00981A(67,000)</t>
+          <t>00403A(500,000)、00407A(700,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00980A(全數賣出)、00407A(-60,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -499,84 +499,84 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00981A(1,300,000)、00985A(新納入)</t>
+          <t>00981A(67,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00980A(全數賣出)</t>
+          <t>00407A(-60,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00981A(2,170,000)、00992A(新納入)</t>
+          <t>00981A(114,000)、00403A(35,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00980A(全數賣出)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00985A(145,000)</t>
+          <t>00981A(190,000)、00407A(100,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00980A(全數賣出)、00407A(-120,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,7 +589,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00403A(500,000)、00407A(700,000)</t>
+          <t>00981A(1,300,000)、00985A(新納入)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -601,12 +601,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -614,29 +614,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00985A(646,000)</t>
+          <t>00981A(2,170,000)、00992A(新納入)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00980A(全數賣出)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,29 +644,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00403A(40,000)</t>
+          <t>00991A(200,000)、00982A(50,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00980A(全數賣出)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -674,227 +674,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00981A(114,000)、00403A(35,000)</t>
+          <t>00985A(145,000)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>禾伸堂</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>00992A(200,000)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>00980A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>00981A(190,000)、00407A(100,000)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>00991A(200,000)、00982A(50,000)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>00403A(11,000)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>00980A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>00980A(全數賣出)、00407A(-150,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>00981A(100,000)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>00980A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>00407A(80,000)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>00980A(全數賣出)</t>
+          <t>00407A(-120,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-10-21_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-21_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,12 +601,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00981A(2,170,000)、00992A(新納入)</t>
+          <t>00991A(200,000)、00982A(50,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,45 +644,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00991A(200,000)、00982A(50,000)</t>
+          <t>00985A(145,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>00985A(145,000)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>00407A(-120,000)</t>
         </is>
